--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17895" windowHeight="8040" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8040"/>
   </bookViews>
   <sheets>
     <sheet name="Mon_Master" sheetId="1" r:id="rId1"/>
     <sheet name="Mon_Effect_Master" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="bjCT6KQnax89l3Ddx+r/Vs6s21SNxp42IHpGT26YCQc="/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Mon_ID</t>
   </si>
@@ -90,12 +90,24 @@
     <t>MonEffect_ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>monster_002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>--</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +142,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -151,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -165,6 +185,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -385,18 +420,18 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="8.375" customWidth="1"/>
-    <col min="4" max="4" width="9.25" customWidth="1"/>
-    <col min="5" max="5" width="8.875" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
-    <col min="9" max="9" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="12" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
     <col min="13" max="26" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -471,13 +506,13 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -490,14 +525,56 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="4" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="5" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="6" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="9" spans="1:26" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:26" ht="16.5" customHeight="1"/>
+    <row r="3" spans="1:26" ht="16.5" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>300</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:26" ht="16.5" customHeight="1">
+      <c r="G4" s="8"/>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:26" ht="16.5" customHeight="1">
+      <c r="G5" s="8"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:26" ht="16.5" customHeight="1">
+      <c r="G6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:26" ht="16.5" customHeight="1">
+      <c r="G7" s="8"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:26" ht="16.5" customHeight="1">
+      <c r="G8" s="8"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:26" ht="16.5" customHeight="1">
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:26" ht="16.5" customHeight="1">
+      <c r="I10" s="8"/>
+    </row>
     <row r="11" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="12" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="13" spans="1:26" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -99,7 +99,20 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>--</t>
+    <r>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -190,9 +203,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -200,6 +210,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,17 +519,17 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>15</v>
+      <c r="J2" s="2">
+        <v>0</v>
       </c>
       <c r="K2" s="2">
         <v>30</v>
@@ -545,35 +558,49 @@
         <v>1.5</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="8"/>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>30</v>
+      </c>
+      <c r="L3">
+        <v>150</v>
+      </c>
     </row>
     <row r="4" spans="1:26" ht="16.5" customHeight="1">
-      <c r="G4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:26" ht="16.5" customHeight="1">
-      <c r="G5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1">
-      <c r="G6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:26" ht="16.5" customHeight="1">
-      <c r="G7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="G7" s="7"/>
+      <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:26" ht="16.5" customHeight="1">
-      <c r="G8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="G8" s="7"/>
+      <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:26" ht="16.5" customHeight="1">
-      <c r="I9" s="8"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:26" ht="16.5" customHeight="1">
-      <c r="I10" s="8"/>
+      <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:26" ht="16.5" customHeight="1"/>
     <row r="12" spans="1:26" ht="16.5" customHeight="1"/>

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCF7F8A-C46F-4242-B9EC-7FC71015EEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Mon_Master" sheetId="1" r:id="rId1"/>
     <sheet name="Mon_Effect_Master" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="bjCT6KQnax89l3Ddx+r/Vs6s21SNxp42IHpGT26YCQc="/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Mon_ID</t>
   </si>
@@ -113,11 +112,15 @@
     <t>골롬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>더미봇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -412,23 +415,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="26" width="7.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="26" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
@@ -525,9 +528,11 @@
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C3">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -536,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>13</v>
@@ -1581,15 +1586,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="7.85546875" customWidth="1"/>
-    <col min="7" max="26" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
+    <col min="3" max="3" width="38.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="7.875" customWidth="1"/>
+    <col min="7" max="26" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -535,7 +535,7 @@
         <v>5000</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -547,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>20</v>

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEOULIT\Documents\Workspace\git\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesk\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AD17DD-B134-4CAB-AB7E-5360C890602C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="7365" yWindow="3915" windowWidth="21090" windowHeight="11580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mon_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Mon_Effect_Master" sheetId="2" r:id="rId2"/>
+    <sheet name="Mon_concentrate" sheetId="3" r:id="rId2"/>
+    <sheet name="Mon_Effect_Master" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,8 +26,558 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>nGle</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{6819000E-6061-4CEF-8900-F1A7571D51F4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MonParts_HP
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몬스터의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>파츠</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>별</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">체력을
+나타낸다
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{BF53669C-6061-445B-A659-50424A80E5E9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MonParts_Hit
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몬스터의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부위를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>타격할</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>확률이다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{62A9227D-4159-4D1C-9D41-64D55A8EEEDB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MonParts_DMG
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몬스터를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>때릴</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>때</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>데미지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>비율</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>계산식</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>총데미지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> = </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>내</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공격력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> + (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>내</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공격력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> * MonParts_DMG)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{F30740C6-8C7C-41BB-87D4-DA218276DCFC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MonParts_Break
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몬스터의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>파츠가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서질</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>때</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>감소되는</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공격력</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Mon_ID</t>
   </si>
@@ -116,12 +668,60 @@
     <t>더미봇</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>MonParts1_Hit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts2_Hit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts3_Hit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts1_DMG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts2_DMG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts3_DMG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts1_HP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts2_HP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts3_HP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts1_Break</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts2_Break</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonParts3_Break</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +758,34 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -200,6 +828,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,23 +1046,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="26" width="7.625" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="26" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
@@ -1586,15 +2217,87 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D475F650-12D1-40B9-93E3-058ED9408AE3}">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="16.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" customWidth="1"/>
-    <col min="3" max="3" width="38.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="7.875" customWidth="1"/>
-    <col min="7" max="26" width="7.625" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="7.85546875" customWidth="1"/>
+    <col min="7" max="26" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwl55\Desktop\PortFolioGM\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03EF806-31D5-4FB2-9EDC-6305E6E208AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7871F8EA-1B19-47E2-A06B-2C4F14636C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2145" yWindow="1125" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mon_Master" sheetId="1" r:id="rId1"/>
@@ -418,21 +418,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="26" width="7.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="26" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1">
@@ -536,19 +536,19 @@
         <v>5000</v>
       </c>
       <c r="D3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>20</v>
@@ -1589,13 +1589,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="25" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.875" customWidth="1"/>
+    <col min="6" max="25" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1">

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7871F8EA-1B19-47E2-A06B-2C4F14636C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6270D-077C-40EB-B677-BA882E625192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1125" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,7 +504,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>21</v>

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6270D-077C-40EB-B677-BA882E625192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54362A9-C721-4717-A692-90480CABA360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="1125" windowWidth="34995" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="4200" windowWidth="38160" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mon_Master" sheetId="1" r:id="rId1"/>

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -538,15 +538,15 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>MonEffect_001</t>
+          <t>Option_009</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_010</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_009</t>
         </is>
       </c>
       <c r="H5" s="1" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_008</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_009</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_008</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_009</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
@@ -814,11 +814,11 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>MonEffect_001</t>
+          <t>Option_014</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>MonEffect_001</t>
+          <t>Option_010</t>
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -906,15 +906,15 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>MonEffect_001</t>
+          <t>Option_013</t>
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>Option_018</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">

--- a/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Monster_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\OneDrive\문서\Unity\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D6A539-2285-4AA6-AC62-164A243D7D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58215942-C080-4353-ABF6-16EE00FC4885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24915" yWindow="1350" windowWidth="21600" windowHeight="12150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mon_Master" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
   <si>
     <t>Mon_ID</t>
   </si>
@@ -161,6 +161,14 @@
     <t>구울</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>Option_009</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Option_010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -216,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -227,6 +235,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -569,17 +580,17 @@
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
+      <c r="G3" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
+      <c r="I3" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="J3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
         <v>30</v>
